--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,218 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>508700</v>
+      </c>
+      <c r="E8" s="3">
         <v>72200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3800</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>45400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>66200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>76100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>392900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>71900</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>261500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>188500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>694800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>429900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>416600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>257500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>255900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>252200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>237200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>220600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>155400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>123000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>138000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>70200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>552400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -910,136 +917,142 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>125400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>115500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>104500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>93600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>87200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>87500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>83000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>86800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>51700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>42000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>39700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>290700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>508700</v>
+      </c>
+      <c r="E10" s="3">
         <v>72200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>47900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3800</v>
       </c>
-      <c r="G10" s="3">
-        <v>-800</v>
-      </c>
       <c r="H10" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I10" s="3">
         <v>45400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>66200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>76100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>392900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>261500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>188500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>569400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>314400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>312100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>163900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>168700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>164700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>154200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>133800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>103700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>81000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>98300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>50600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>261700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,180 +1259,189 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E14" s="3">
         <v>14200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-46600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4600</v>
       </c>
-      <c r="G14" s="3">
-        <v>2100</v>
-      </c>
       <c r="H14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I14" s="3">
         <v>4400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-10000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-40200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-277800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>10100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>133400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>16900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>43300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1426800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>471900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E15" s="3">
         <v>5300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>8200</v>
       </c>
       <c r="J15" s="3">
         <v>8200</v>
       </c>
       <c r="K15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L15" s="3">
         <v>8100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>44300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>145600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>155400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>128600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>132900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>129200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>138200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>139400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>85600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>80600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>74800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>38100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>110100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>270800</v>
+      </c>
+      <c r="E17" s="3">
         <v>51100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>58900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17600</v>
       </c>
-      <c r="G17" s="3">
-        <v>26000</v>
-      </c>
       <c r="H17" s="3">
+        <v>23700</v>
+      </c>
+      <c r="I17" s="3">
         <v>47000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>62100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>70400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>267200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>75400</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>151800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>124100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>741500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>468400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>483400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>501200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>280400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>304100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>308600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>390100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>241100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>188900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>624600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>161900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1036000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>237900</v>
+      </c>
+      <c r="E18" s="3">
         <v>21200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-26900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>125600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>109700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>64400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-46700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-38500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-66800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-243700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-24500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-51900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-71400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-169500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-85700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-65900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-486600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-91700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-483600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,53 +1680,54 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
-        <v>-7000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5900</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>22300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>153000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1725,147 +1759,153 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>247900</v>
+      </c>
+      <c r="E21" s="3">
         <v>30500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-11300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I21" s="3">
         <v>5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>141700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>96700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>72400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-165600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>532600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>107100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>88500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-112800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>113500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>86200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>98700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>20800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>53100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>100600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-213600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>45700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-364300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E22" s="3">
         <v>3500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5200</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>5500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1905,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>238300</v>
+      </c>
+      <c r="E23" s="3">
         <v>7500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-26600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>47800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>130600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15400</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>359700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-180600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-46700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-38500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-66800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-243700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-24500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-51900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-71400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-169500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-85700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-65900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-486600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-483700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>4900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-7400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-11000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-75200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-18700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-13200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-15100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>237400</v>
+      </c>
+      <c r="E26" s="3">
         <v>7500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>46900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>130700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16600</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>359600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>43000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-181700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-59800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-64300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-236300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-33400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-40900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-146300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-67000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-471500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-86500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-483900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>209200</v>
+      </c>
+      <c r="E27" s="3">
         <v>5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>49300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16400</v>
       </c>
-      <c r="G27" s="3">
-        <v>16700</v>
-      </c>
       <c r="H27" s="3">
+        <v>16600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>75300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-42900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>257000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-212500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-190100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-49500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-169200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-27100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-104300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-42400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-36200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-432200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-83200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-453100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,94 +2479,100 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E29" s="3">
         <v>-5500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-1700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>1600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-4200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-5500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-14100</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-80900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-95500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-110600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-192200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-35300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-54300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-93100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-16400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>68100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-128700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-160500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-97000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-169600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-279700</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>426000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,53 +2746,56 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
-        <v>7000</v>
-      </c>
       <c r="H32" s="3">
+        <v>9100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5900</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>-22300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-153000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2757,102 +2827,108 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E33" s="3">
         <v>20000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>65100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>31600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>91400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29600</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>276500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-197800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-382300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-84800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-49000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-262300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-20700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>41000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-141300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-264800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-139300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-205800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-362900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E35" s="3">
         <v>20000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>65100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>31600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>91400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29600</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>276500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-197800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-382300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-84800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-49000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-262300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-20700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>41000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-141300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-264800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-139300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-205800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-362900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>508200</v>
+      </c>
+      <c r="E41" s="3">
         <v>411300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>382500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>358400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>340700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>349900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>302200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>294400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>261200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>247400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>345300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>434000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>426900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>668500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>918300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>636400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>337200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1117700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1602100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1277700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1006200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>788400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>703500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>658400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1099500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1361800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1205200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3350,94 +3440,100 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E43" s="3">
         <v>125500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>99100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>102700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>114100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>127200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>103000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>94800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>94700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>153000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>182100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>173300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>126300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>158900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>141900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>155200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>143600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>112700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>94600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>150600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>169300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>145100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>154300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>179300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>212700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3480,8 +3576,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3522,139 +3618,145 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E45" s="3">
         <v>10300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>91700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>67200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>58000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>67300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>62400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>75400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>61900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>97400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>107100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>86700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>84600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>107900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>113100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>618400</v>
+      </c>
+      <c r="E46" s="3">
         <v>553100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>607200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>474600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>457200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>478100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>441400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>412800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>382500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>361400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>463700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>723500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>855400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1064700</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3694,266 +3796,278 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2612700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2241500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2266400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2463500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2389800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2388600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2492300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2540000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2517700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2488800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2476100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1880000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1288900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1227000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1460000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1224700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1594400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1445300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1109100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>905300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>873100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>863100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3032800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3237100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3223500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3766400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3866600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E48" s="3">
         <v>26500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>40200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3093400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6614700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6425900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6385200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6815500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6741100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6119700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5470900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5433400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5027300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8252500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9354900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8067900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9218300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10704000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11125800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>504300</v>
+      </c>
+      <c r="E49" s="3">
         <v>509000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>514000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>519900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>526700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>532100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>538100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>547300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>553300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>560700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>569700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>576900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1197800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1196700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1853500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2506900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2589300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1986900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1949000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2002400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1992000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2153900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2367900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2126800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1417000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1969100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2091700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E52" s="3">
         <v>3900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>176000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>206600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>265400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>257600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3775700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5559100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6782500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4221300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4268900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4549100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>853600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>918200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1076800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3763500</v>
+      </c>
+      <c r="E54" s="3">
         <v>3334000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3419200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3490500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3408600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3439000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3513300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3542900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3502400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3463800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3562600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6872100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10757100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10743400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11028500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11740800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11877300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11232200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14197800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15443000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15921300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16625300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20200600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19043100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16183500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19160100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19832200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,94 +4576,98 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E57" s="3">
         <v>57600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>38300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>38700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>219400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>185900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>188700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>192000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>114700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>121900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>129400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>83200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>109300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>178400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>113100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>132400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>170700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>177900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4541,11 +4675,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>9900</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -4618,139 +4752,145 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>147200</v>
+      </c>
+      <c r="E59" s="3">
         <v>135300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>122300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>93700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>86100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>76600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>72200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>84700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>81700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>73600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>78700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>88000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>71800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>847100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>998400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>917300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>528300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>570900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>601800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>516800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>494900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>580800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>318100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>374800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>390000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>511200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>758000</v>
+      </c>
+      <c r="E60" s="3">
         <v>544000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>604100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>545900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>577800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>606400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>650500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>657000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>663300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>481600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>510400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>428100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>521700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>494000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4790,180 +4930,189 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>319700</v>
+      </c>
+      <c r="E61" s="3">
         <v>329200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>321100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>362100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>335200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>340200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>339700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>340700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>339800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>412600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>420800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3207100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5835400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5782200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5291800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5463100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5679000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5264300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5003200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4714800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4022800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7024000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7938700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7086000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9211100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9453300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9386800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E62" s="3">
         <v>15300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>28900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>111900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>166500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>140400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>134600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>224000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>238900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3090700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3837400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4732900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2059600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3865900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4079400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>457100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>469800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>490400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1117200</v>
+      </c>
+      <c r="E66" s="3">
         <v>914600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>969000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>971400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>957800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>974300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1022100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1036600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1039700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>941400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1053400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3846800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6596100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6484200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9367800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10086200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10244000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9841300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12050900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13387100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13812400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14403200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17699100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16457500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13443800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14413600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14616100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5552,16 +5720,16 @@
         <v>794700</v>
       </c>
       <c r="P70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="Q70" s="3">
         <v>800300</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>800400</v>
       </c>
       <c r="R70" s="3">
         <v>800400</v>
       </c>
       <c r="S70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="T70" s="3">
         <v>854200</v>
@@ -5570,10 +5738,10 @@
         <v>854200</v>
       </c>
       <c r="V70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="W70" s="3">
         <v>916100</v>
-      </c>
-      <c r="W70" s="3">
-        <v>999500</v>
       </c>
       <c r="X70" s="3">
         <v>999500</v>
@@ -5594,10 +5762,13 @@
         <v>999500</v>
       </c>
       <c r="AD70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="AE70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6547200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6758000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6761500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6810100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6825000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6840100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6837500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6816100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6813400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6888500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1550800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1312200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1312600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1257400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1223900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1166100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1163900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1185600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1177800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1023800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1016400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>896100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>647500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>652000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>860300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>854300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>779100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>536600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1292700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1139800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1109500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1222500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1502000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1586100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1740300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3746900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4216600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E81" s="3">
         <v>20000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>65100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>31600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>91400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29600</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>276500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-197800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-382300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-84800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-49000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-262300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-20700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>41000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-141300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-264800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-139300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-205800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-362900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,13 +6605,14 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
@@ -6425,76 +6624,79 @@
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>119200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>138700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>135400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-266000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>110800</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>85700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>579300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>145600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>155400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>130900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>138000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>138100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>170100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>190300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>138800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>166400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>273000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>137500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>119400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-40000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>75600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>56500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>77000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>50300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>35900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>100200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>72100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>262600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>120700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>72800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>66800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>76500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>128800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-23900</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>47600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>42300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-59700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-63700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,41 +7261,42 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-300</v>
       </c>
       <c r="I91" s="3">
         <v>-300</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3100</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
@@ -7085,8 +7306,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E94" s="3">
         <v>101400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-86000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>17500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-196500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-312400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-259100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1913400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>216300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>60900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-322900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>416500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-950100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>114600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>166900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>5136600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7435,7 +7669,7 @@
         <v>1800</v>
       </c>
       <c r="H96" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="I96" s="3">
         <v>1700</v>
@@ -7447,13 +7681,13 @@
         <v>1700</v>
       </c>
       <c r="L96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M96" s="3">
         <v>1600</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N96" s="3">
-        <v>1600</v>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>1600</v>
@@ -7462,11 +7696,11 @@
         <v>1600</v>
       </c>
       <c r="Q96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1600</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -7492,10 +7726,10 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-53700</v>
       </c>
       <c r="AC96" s="3">
         <v>-53700</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-15900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-48500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>54500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>26800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>923800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-18600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>201000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>559300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>213000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>506900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-407900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>99200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1009800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>692700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-329500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>97400</v>
+      </c>
+      <c r="E102" s="3">
         <v>21900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>31500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>47800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>32600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-98100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-42900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-242600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-212500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-729500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>324600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-778200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-542200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>337300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>254800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>139700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>71400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>63600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-350200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-175100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>108500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>695600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>35300</v>
       </c>
     </row>
